--- a/workbooks/control_matrix.xlsx
+++ b/workbooks/control_matrix.xlsx
@@ -1,45 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saarthaksharma/Security_Risk_Register/Security-Risk-Register/workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D7A7BC-C4F4-6A40-AED0-032E70547782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50878788-42B0-7341-A1B6-F4498CF986A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37920" yWindow="960" windowWidth="28040" windowHeight="17180" xr2:uid="{32F89278-E50A-C944-AB5D-4BD0BA4F3A9A}"/>
+    <workbookView xWindow="42280" yWindow="2060" windowWidth="18200" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="131">
   <si>
     <t>Control ID</t>
   </si>
@@ -78,6 +59,360 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>AC-01</t>
+  </si>
+  <si>
+    <t>Quarterly User Access Reviews</t>
+  </si>
+  <si>
+    <t>NIST CSF PR.AA, CIS 6</t>
+  </si>
+  <si>
+    <t>Access Management</t>
+  </si>
+  <si>
+    <t>Ensure user access is reviewed regularly and remains appropriate based on job responsibilities.</t>
+  </si>
+  <si>
+    <t>IT Operations</t>
+  </si>
+  <si>
+    <t>User access export, access review sign-off, manager approval evidence</t>
+  </si>
+  <si>
+    <t>Review user access export and confirm documented manager approval for sampled users.</t>
+  </si>
+  <si>
+    <t>Partial Pass</t>
+  </si>
+  <si>
+    <t>Access review evidence is incomplete for several users.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Require documented manager approval for all reviewed users and retain evidence in a central location.</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>AC-02</t>
+  </si>
+  <si>
+    <t>Terminated User Access Removal</t>
+  </si>
+  <si>
+    <t>NIST CSF PR.AA, CIS 5</t>
+  </si>
+  <si>
+    <t>Ensure terminated users are removed from business systems in a timely manner.</t>
+  </si>
+  <si>
+    <t>HR termination report, Jira access export, GitHub access export</t>
+  </si>
+  <si>
+    <t>Compare terminated user list against active application access exports.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Two terminated users retained active application access after termination.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Remove access immediately and implement weekly HR-to-access reconciliation.</t>
+  </si>
+  <si>
+    <t>AC-03</t>
+  </si>
+  <si>
+    <t>Privileged Access Approval</t>
+  </si>
+  <si>
+    <t>Ensure privileged access is approved, documented, and limited to authorized users.</t>
+  </si>
+  <si>
+    <t>IT Security</t>
+  </si>
+  <si>
+    <t>Privileged access list, manager approval records, admin group export</t>
+  </si>
+  <si>
+    <t>Review privileged access accounts and verify documented approval evidence.</t>
+  </si>
+  <si>
+    <t>Some privileged accounts are missing approval documentation.</t>
+  </si>
+  <si>
+    <t>Require approval evidence for all privileged access and review admin access quarterly.</t>
+  </si>
+  <si>
+    <t>IA-01</t>
+  </si>
+  <si>
+    <t>MFA Enforcement</t>
+  </si>
+  <si>
+    <t>Identity and Authentication</t>
+  </si>
+  <si>
+    <t>Ensure MFA is enforced for all active users accessing company systems.</t>
+  </si>
+  <si>
+    <t>MFA policy screenshot, active user export, conditional access policy</t>
+  </si>
+  <si>
+    <t>Review MFA policy and compare covered users against active user list.</t>
+  </si>
+  <si>
+    <t>MFA is enabled for most users but exceptions are not fully documented.</t>
+  </si>
+  <si>
+    <t>Document MFA exceptions and require periodic review of excluded users.</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>IA-02</t>
+  </si>
+  <si>
+    <t>Password Policy Enforcement</t>
+  </si>
+  <si>
+    <t>NIST CSF PR.AA</t>
+  </si>
+  <si>
+    <t>Ensure password requirements align with company authentication standards.</t>
+  </si>
+  <si>
+    <t>Password policy screenshot, authentication settings export</t>
+  </si>
+  <si>
+    <t>Review password policy settings for length, complexity, lockout, and expiration requirements.</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Password policy is documented and enforced across active users.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Continue periodic review of authentication settings.</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>AU-01</t>
+  </si>
+  <si>
+    <t>Audit Logging Enabled</t>
+  </si>
+  <si>
+    <t>NIST CSF DE.CM, CIS 8</t>
+  </si>
+  <si>
+    <t>Logging and Monitoring</t>
+  </si>
+  <si>
+    <t>Ensure key system activity is logged to support monitoring and investigations.</t>
+  </si>
+  <si>
+    <t>Security Operations</t>
+  </si>
+  <si>
+    <t>Logging configuration screenshot, sample audit logs, retention settings</t>
+  </si>
+  <si>
+    <t>Review logging settings and confirm key systems generate audit logs.</t>
+  </si>
+  <si>
+    <t>Logging is enabled, but retention requirements are not clearly documented.</t>
+  </si>
+  <si>
+    <t>Document log retention requirements and review logging coverage quarterly.</t>
+  </si>
+  <si>
+    <t>RA-01</t>
+  </si>
+  <si>
+    <t>Vulnerability Remediation Tracking</t>
+  </si>
+  <si>
+    <t>NIST CSF ID.RA, CIS 7</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
+    <t>Ensure vulnerabilities are tracked, assigned owners, and remediated based on severity.</t>
+  </si>
+  <si>
+    <t>Vulnerability scan report, remediation tracker, SLA policy</t>
+  </si>
+  <si>
+    <t>Review vulnerability findings and compare remediation dates against SLA requirements.</t>
+  </si>
+  <si>
+    <t>Critical and high findings are not consistently tracked against SLA due dates.</t>
+  </si>
+  <si>
+    <t>Implement SLA-based remediation tracking with owner, due date, and status fields.</t>
+  </si>
+  <si>
+    <t>CM-01</t>
+  </si>
+  <si>
+    <t>Change Approval Required</t>
+  </si>
+  <si>
+    <t>NIST CSF GV.OV, CIS 4</t>
+  </si>
+  <si>
+    <t>Change Management</t>
+  </si>
+  <si>
+    <t>Ensure production changes are reviewed and approved before implementation.</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Change tickets, approval records, release notes</t>
+  </si>
+  <si>
+    <t>Sample recent production changes and verify approval evidence exists.</t>
+  </si>
+  <si>
+    <t>Some change tickets are missing approval evidence.</t>
+  </si>
+  <si>
+    <t>Require approval documentation before production promotion.</t>
+  </si>
+  <si>
+    <t>IR-01</t>
+  </si>
+  <si>
+    <t>Incident Response Plan Maintained</t>
+  </si>
+  <si>
+    <t>NIST CSF RS, CIS 17</t>
+  </si>
+  <si>
+    <t>Incident Response</t>
+  </si>
+  <si>
+    <t>Ensure the organization has a documented incident response plan.</t>
+  </si>
+  <si>
+    <t>Incident response plan, tabletop exercise notes, contact list</t>
+  </si>
+  <si>
+    <t>Review incident response documentation and confirm plan ownership.</t>
+  </si>
+  <si>
+    <t>Incident response plan is documented and has assigned owners.</t>
+  </si>
+  <si>
+    <t>Schedule annual tabletop exercise and document lessons learned.</t>
+  </si>
+  <si>
+    <t>CP-01</t>
+  </si>
+  <si>
+    <t>Backup Testing Performed</t>
+  </si>
+  <si>
+    <t>NIST CSF RC, CIS 11</t>
+  </si>
+  <si>
+    <t>Business Continuity</t>
+  </si>
+  <si>
+    <t>Ensure backups are tested to support recovery of critical systems.</t>
+  </si>
+  <si>
+    <t>Backup policy, backup logs, restore test evidence</t>
+  </si>
+  <si>
+    <t>Review backup evidence and confirm restore testing was performed.</t>
+  </si>
+  <si>
+    <t>Backups are configured, but restore test evidence is incomplete.</t>
+  </si>
+  <si>
+    <t>Document restore testing results and retain evidence quarterly.</t>
+  </si>
+  <si>
+    <t>AT-01</t>
+  </si>
+  <si>
+    <t>Security Awareness Training</t>
+  </si>
+  <si>
+    <t>NIST CSF PR.AT, CIS 14</t>
+  </si>
+  <si>
+    <t>Training and Awareness</t>
+  </si>
+  <si>
+    <t>Ensure employees complete required security awareness training.</t>
+  </si>
+  <si>
+    <t>HR / Security</t>
+  </si>
+  <si>
+    <t>Training completion report, training policy, user roster</t>
+  </si>
+  <si>
+    <t>Compare training completion report against active employee list.</t>
+  </si>
+  <si>
+    <t>Training completion is documented for active employees.</t>
+  </si>
+  <si>
+    <t>Continue annual training and retain completion reports.</t>
+  </si>
+  <si>
+    <t>VR-01</t>
+  </si>
+  <si>
+    <t>Vendor Security Review</t>
+  </si>
+  <si>
+    <t>NIST CSF GV.SC, CIS 15</t>
+  </si>
+  <si>
+    <t>Third-Party Risk</t>
+  </si>
+  <si>
+    <t>Ensure vendors are reviewed for security and compliance risks before onboarding.</t>
+  </si>
+  <si>
+    <t>Procurement / Security</t>
+  </si>
+  <si>
+    <t>Vendor questionnaire, contract terms, security review notes</t>
+  </si>
+  <si>
+    <t>Review vendor documentation for data protection, incident response, and access controls.</t>
+  </si>
+  <si>
+    <t>Vendor review was completed, but breach notification terms are unclear.</t>
+  </si>
+  <si>
+    <t>Update vendor review checklist to include breach notification and data handling requirements.</t>
   </si>
 </sst>
 </file>
@@ -86,9 +421,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -113,14 +448,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -167,20 +503,20 @@
         <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -208,31 +544,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -260,23 +579,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -288,171 +590,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB47AEB-DB82-104F-B3EF-9C81649EB0F5}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="13" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -491,6 +802,498 @@
       </c>
       <c r="M1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>73</v>
+      </c>
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" t="s">
+        <v>101</v>
+      </c>
+      <c r="M10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>110</v>
+      </c>
+      <c r="M11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H12" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" t="s">
+        <v>127</v>
+      </c>
+      <c r="H13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" t="s">
+        <v>130</v>
+      </c>
+      <c r="M13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
